--- a/Input/Allianz_Expat_Protect/benefits.xlsx
+++ b/Input/Allianz_Expat_Protect/benefits.xlsx
@@ -271,7 +271,7 @@
     <t xml:space="preserve">Annually</t>
   </si>
   <si>
-    <t xml:space="preserve">Zone 1</t>
+    <t xml:space="preserve">Nzone1</t>
   </si>
   <si>
     <t xml:space="preserve">Out-patient Consultations/Out-patient Specialists/Out-patient Medicines/Vaccination/Scans &amp; Diagnostic Tests/Physiotherapy/Optical Benefits/Wellness &amp; Health Screening/Alternative Medicines/Mental Health Benefit</t>
@@ -433,7 +433,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BD13"/>
-  <sheetFormatPr defaultColWidth="8.51953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5234375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="0" width="39.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="1" width="52.24"/>
